--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chank\Desktop\humankind\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5956AB7-F446-41C7-B24E-3B965D0E8E67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AE03DF1-5FF5-4C93-9033-D4C15797D11B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{9A20E045-E396-46C7-936F-ACE9DDE93956}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="62">
   <si>
     <t>초원</t>
   </si>
@@ -134,12 +134,6 @@
     <t>바다1</t>
   </si>
   <si>
-    <t>숲1</t>
-  </si>
-  <si>
-    <t>열대우림1</t>
-  </si>
-  <si>
     <t>사막1</t>
   </si>
   <si>
@@ -177,6 +171,57 @@
   </si>
   <si>
     <t xml:space="preserve">소모하여 지형 </t>
+  </si>
+  <si>
+    <t>초원2(식4)</t>
+  </si>
+  <si>
+    <t>초원3(식6)</t>
+  </si>
+  <si>
+    <t>초원4(식8)</t>
+  </si>
+  <si>
+    <t>초원5(식10)</t>
+  </si>
+  <si>
+    <t>평원2(식3,골1)</t>
+  </si>
+  <si>
+    <t>평원3(식5,골2)</t>
+  </si>
+  <si>
+    <t>평원4(식6,골3)</t>
+  </si>
+  <si>
+    <t>평원5(식6,골5)</t>
+  </si>
+  <si>
+    <t>숲1(식2)</t>
+  </si>
+  <si>
+    <t>숲2(식4)</t>
+  </si>
+  <si>
+    <t>숲3(식6,골1)</t>
+  </si>
+  <si>
+    <t>숲4(식7,골2)</t>
+  </si>
+  <si>
+    <t>숲5(식8,골3)</t>
+  </si>
+  <si>
+    <t>숲6(식8,골4)</t>
+  </si>
+  <si>
+    <t>열대우림2(식4)</t>
+  </si>
+  <si>
+    <t>열대우림1(식2)</t>
+  </si>
+  <si>
+    <t>열대우림3(식6)</t>
   </si>
 </sst>
 </file>
@@ -192,12 +237,42 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -212,8 +287,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -556,7 +636,9 @@
     <col min="3" max="3" width="13.28515625" customWidth="1"/>
     <col min="4" max="4" width="15.28515625" customWidth="1"/>
     <col min="5" max="5" width="14.7109375" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" customWidth="1"/>
+    <col min="7" max="7" width="15.5703125" customWidth="1"/>
+    <col min="8" max="9" width="14" customWidth="1"/>
     <col min="19" max="19" width="9.85546875" customWidth="1"/>
     <col min="20" max="20" width="43.140625" customWidth="1"/>
     <col min="21" max="21" width="19.5703125" customWidth="1"/>
@@ -576,7 +658,7 @@
     </row>
     <row r="2" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="S2" t="s">
         <v>1</v>
@@ -590,7 +672,7 @@
     </row>
     <row r="3" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="S3" t="s">
         <v>2</v>
@@ -606,8 +688,8 @@
       <c r="B4">
         <v>0</v>
       </c>
-      <c r="C4" t="s">
-        <v>38</v>
+      <c r="C4" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="S4" t="s">
         <v>3</v>
@@ -626,20 +708,20 @@
       <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" t="s">
-        <v>40</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="C5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" t="s">
         <v>33</v>
-      </c>
-      <c r="H5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I5" t="s">
-        <v>35</v>
       </c>
       <c r="S5" t="s">
         <v>4</v>
@@ -661,8 +743,8 @@
       <c r="E6" t="s">
         <v>31</v>
       </c>
-      <c r="F6" t="s">
-        <v>32</v>
+      <c r="F6" s="5" t="s">
+        <v>53</v>
       </c>
       <c r="S6" t="s">
         <v>5</v>
@@ -709,11 +791,14 @@
       <c r="B9">
         <v>5</v>
       </c>
+      <c r="C9" s="4" t="s">
+        <v>45</v>
+      </c>
       <c r="S9" t="s">
         <v>19</v>
       </c>
       <c r="T9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="U9" t="s">
         <v>20</v>
@@ -723,11 +808,17 @@
       <c r="B10">
         <v>6</v>
       </c>
+      <c r="D10" s="3" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="11" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>7</v>
       </c>
+      <c r="F11" s="5" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="12" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B12">
@@ -738,40 +829,52 @@
       <c r="B13">
         <v>9</v>
       </c>
+      <c r="G13" s="2" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B14">
         <v>10</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="1" t="s">
         <v>28</v>
       </c>
       <c r="S14" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B15">
         <v>11</v>
       </c>
+      <c r="C15" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="T15" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B16">
         <v>12</v>
       </c>
+      <c r="F16" s="5" t="s">
+        <v>55</v>
+      </c>
       <c r="T16" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B17">
         <v>13</v>
       </c>
+      <c r="D17" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="T17" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="2:20" x14ac:dyDescent="0.25">
@@ -779,7 +882,7 @@
         <v>14</v>
       </c>
       <c r="T18" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.25">
@@ -791,16 +894,28 @@
       <c r="B20">
         <v>16</v>
       </c>
+      <c r="C20" s="4" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="21" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B21">
         <v>17</v>
       </c>
+      <c r="F21" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="22" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B22">
         <v>18</v>
       </c>
+      <c r="D22" s="3" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="23" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B23">
@@ -811,7 +926,7 @@
       <c r="B24">
         <v>20</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="1" t="s">
         <v>29</v>
       </c>
     </row>
@@ -824,16 +939,25 @@
       <c r="B26">
         <v>22</v>
       </c>
+      <c r="F26" s="5" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="27" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B27">
         <v>23</v>
       </c>
+      <c r="C27" s="4" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="28" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B28">
         <v>24</v>
       </c>
+      <c r="D28" s="3" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="29" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B29">
@@ -848,6 +972,9 @@
     <row r="31" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B31">
         <v>27</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="32" spans="2:20" x14ac:dyDescent="0.25">
